--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -438,7 +438,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -508,7 +508,7 @@
     <t>Extension.value[x].assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -849,7 +849,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="20.21875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="24.74609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -864,7 +864,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="37.421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="38.1484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -438,7 +438,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -508,7 +508,7 @@
     <t>Extension.value[x].assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -849,7 +849,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="24.74609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="20.21875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -864,7 +864,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="38.1484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="37.421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
